--- a/Plots/Racial-Gender-Imbalance.xlsx
+++ b/Plots/Racial-Gender-Imbalance.xlsx
@@ -5,21 +5,22 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\subir\OneDrive\Documents\github_large\Plots\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5adae42a5ff17c16/Documents/GitHub/Diffusion/Plots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26C72A6-538E-46C6-AA8D-2A1B66CCFA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="371" documentId="13_ncr:1_{B26C72A6-538E-46C6-AA8D-2A1B66CCFA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C750E041-7AF1-4B62-AC73-91BC5BE50002}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{F67D4908-C1D3-42DC-AAAE-E71A5B929D9F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F67D4908-C1D3-42DC-AAAE-E71A5B929D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="4" r:id="rId1"/>
     <sheet name="CelebA-HQ" sheetId="1" r:id="rId2"/>
     <sheet name="plot" sheetId="5" r:id="rId3"/>
+    <sheet name="plot2" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="26" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="26">
   <si>
     <t>Dataset</t>
   </si>
@@ -94,6 +95,30 @@
   <si>
     <t>Sum of generation in percentage</t>
   </si>
+  <si>
+    <t>Models</t>
+  </si>
+  <si>
+    <t>CelebA</t>
+  </si>
+  <si>
+    <t>FairFace</t>
+  </si>
+  <si>
+    <t>Bal-FairFace</t>
+  </si>
+  <si>
+    <t>sigma</t>
+  </si>
+  <si>
+    <t>Std. dev</t>
+  </si>
+  <si>
+    <t>CelebA-HQ</t>
+  </si>
+  <si>
+    <t>_</t>
+  </si>
 </sst>
 </file>
 
@@ -128,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -140,7 +165,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -736,9 +764,2715 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>plot2!$N$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Dataset</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>plot2!$O$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Std. dev</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>plot2!$O$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.18190244638266961</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9FD0-4924-958B-DCF28915AC73}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>plot2!$N$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DDPM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>plot2!$O$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Std. dev</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>plot2!$O$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.21023346397517212</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9FD0-4924-958B-DCF28915AC73}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>plot2!$N$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DDGAN</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>plot2!$O$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Std. dev</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>plot2!$O$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.1854865224214417</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9FD0-4924-958B-DCF28915AC73}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>plot2!$N$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LDM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>plot2!$O$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Std. dev</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>plot2!$O$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.20701569988771382</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-9FD0-4924-958B-DCF28915AC73}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="382750128"/>
+        <c:axId val="387302432"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="382750128"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="387302432"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="387302432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="382750128"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>plot2!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CelebA-HQ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>plot2!$C$1:$J$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="8"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>White</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Black</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Indian</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Asian</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>plot2!$C$3:$J$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.28699999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1986-4532-8052-029B7CF8F51B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>plot2!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DDPM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>plot2!$C$1:$J$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="8"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>White</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Black</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Indian</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Asian</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>plot2!$C$4:$J$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.64400000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.248</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1986-4532-8052-029B7CF8F51B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>plot2!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DDGAN</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>plot2!$C$1:$J$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="8"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>White</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Black</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Indian</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Asian</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>plot2!$C$5:$J$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.57899999999999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.0000000000000001E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1986-4532-8052-029B7CF8F51B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>plot2!$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LDM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>plot2!$C$1:$J$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="8"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>White</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Black</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Indian</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Asian</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>plot2!$C$6:$J$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.61899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.28799999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.9999999999999993E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-1986-4532-8052-029B7CF8F51B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="440894752"/>
+        <c:axId val="387308880"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="440894752"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="387308880"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="387308880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="440894752"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>plot2!$B$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FairFace</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>plot2!$C$8:$J$9</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="8"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>White</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Black</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Indian</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Asian</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>plot2!$C$10:$J$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.189</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.113</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.14899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-57DD-4449-9016-83A445B7F5FA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>plot2!$B$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DDPM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>plot2!$C$8:$J$9</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="8"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>White</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Black</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Indian</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Asian</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>plot2!$C$11:$J$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.29099999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.216</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.19700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.13600000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-57DD-4449-9016-83A445B7F5FA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>plot2!$B$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DDGAN</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>plot2!$C$8:$J$9</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="8"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>White</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Black</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Indian</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Asian</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>plot2!$C$12:$J$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.124</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.112</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.22500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.21099999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-57DD-4449-9016-83A445B7F5FA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>plot2!$B$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LDM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>plot2!$C$8:$J$9</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="8"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>White</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Black</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Indian</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Asian</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>plot2!$C$13:$J$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-57DD-4449-9016-83A445B7F5FA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="741565232"/>
+        <c:axId val="746460240"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="741565232"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="746460240"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="746460240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="741565232"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>plot2!$B$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Bal-FairFace</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>plot2!$C$15:$J$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="8"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>White</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Black</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Indian</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Asian</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>plot2!$C$17:$J$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.125</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-469A-4A52-ADC7-AE39796291E8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>plot2!$B$18</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DDPM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>plot2!$C$15:$J$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="8"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>White</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Black</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Indian</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Asian</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>plot2!$C$18:$J$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.249</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.17299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.4000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.14699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.11799999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-469A-4A52-ADC7-AE39796291E8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>plot2!$B$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DDGAN</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>plot2!$C$15:$J$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="8"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>White</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Black</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Indian</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Asian</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>plot2!$C$19:$J$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.11899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.11600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.193</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.153</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.14399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.9000000000000005E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-469A-4A52-ADC7-AE39796291E8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>plot2!$B$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LDM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>plot2!$C$15:$J$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="8"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Female</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Male</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>White</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Black</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Indian</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Asian</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>plot2!$C$20:$J$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-469A-4A52-ADC7-AE39796291E8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="741555152"/>
+        <c:axId val="746457264"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="741555152"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="746457264"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="746457264"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="741555152"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="21">
   <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -1206,6 +3940,2018 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx2"/>
     </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -1243,6 +5989,155 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>334530</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>53109</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>29730</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>34059</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{197CA70B-D345-A0E2-C93B-3CDD9F2E44AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>80818</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>408709</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>61191</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDC6E572-86AC-068F-95CA-DE2F2FB93E0F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>151535</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>98426</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A177F35-11EC-DE8F-BF4C-0B949FD33F21}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>294120</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>53686</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>598921</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>34636</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D19A7337-DAF0-EEF4-03A0-CB809C318521}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1498,7 +6393,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EB6C171A-9B06-4D87-8649-64E15081FE89}" name="PivotTable13" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EB6C171A-9B06-4D87-8649-64E15081FE89}" name="PivotTable13" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B59" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
@@ -2040,7 +6935,7 @@
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>55</v>
       </c>
     </row>
@@ -2048,7 +6943,7 @@
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>4</v>
       </c>
     </row>
@@ -2056,7 +6951,7 @@
       <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>2</v>
       </c>
     </row>
@@ -2064,7 +6959,7 @@
       <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>2</v>
       </c>
     </row>
@@ -2072,7 +6967,7 @@
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8">
         <v>10</v>
       </c>
     </row>
@@ -2080,7 +6975,7 @@
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9">
         <v>5</v>
       </c>
     </row>
@@ -2088,7 +6983,7 @@
       <c r="A10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10">
         <v>5</v>
       </c>
     </row>
@@ -2096,7 +6991,7 @@
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11">
         <v>6</v>
       </c>
     </row>
@@ -2104,7 +6999,7 @@
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12">
         <v>3</v>
       </c>
     </row>
@@ -2112,7 +7007,7 @@
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13">
         <v>3</v>
       </c>
     </row>
@@ -2120,7 +7015,7 @@
       <c r="A14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14">
         <v>35</v>
       </c>
     </row>
@@ -2128,7 +7023,7 @@
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15">
         <v>15</v>
       </c>
     </row>
@@ -2136,7 +7031,7 @@
       <c r="A16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16">
         <v>20</v>
       </c>
     </row>
@@ -2144,7 +7039,7 @@
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17">
         <v>83</v>
       </c>
     </row>
@@ -2152,7 +7047,7 @@
       <c r="A18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18">
         <v>12</v>
       </c>
     </row>
@@ -2160,7 +7055,7 @@
       <c r="A19" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19">
         <v>6</v>
       </c>
     </row>
@@ -2168,7 +7063,7 @@
       <c r="A20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20">
         <v>6</v>
       </c>
     </row>
@@ -2176,7 +7071,7 @@
       <c r="A21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21">
         <v>8</v>
       </c>
     </row>
@@ -2184,7 +7079,7 @@
       <c r="A22" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22">
         <v>4</v>
       </c>
     </row>
@@ -2192,7 +7087,7 @@
       <c r="A23" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23">
         <v>4</v>
       </c>
     </row>
@@ -2200,7 +7095,7 @@
       <c r="A24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24">
         <v>8</v>
       </c>
     </row>
@@ -2208,7 +7103,7 @@
       <c r="A25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25">
         <v>4</v>
       </c>
     </row>
@@ -2216,7 +7111,7 @@
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26">
         <v>4</v>
       </c>
     </row>
@@ -2224,7 +7119,7 @@
       <c r="A27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27">
         <v>55</v>
       </c>
     </row>
@@ -2232,7 +7127,7 @@
       <c r="A28" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28">
         <v>25</v>
       </c>
     </row>
@@ -2240,7 +7135,7 @@
       <c r="A29" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29">
         <v>30</v>
       </c>
     </row>
@@ -2248,7 +7143,7 @@
       <c r="A30" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30">
         <v>103</v>
       </c>
     </row>
@@ -2256,7 +7151,7 @@
       <c r="A31" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31">
         <v>20</v>
       </c>
     </row>
@@ -2264,7 +7159,7 @@
       <c r="A32" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32">
         <v>10</v>
       </c>
     </row>
@@ -2272,7 +7167,7 @@
       <c r="A33" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33">
         <v>10</v>
       </c>
     </row>
@@ -2280,7 +7175,7 @@
       <c r="A34" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34">
         <v>4</v>
       </c>
     </row>
@@ -2288,7 +7183,7 @@
       <c r="A35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35">
         <v>2</v>
       </c>
     </row>
@@ -2296,7 +7191,7 @@
       <c r="A36" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36">
         <v>2</v>
       </c>
     </row>
@@ -2304,7 +7199,7 @@
       <c r="A37" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37">
         <v>4</v>
       </c>
     </row>
@@ -2312,7 +7207,7 @@
       <c r="A38" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38">
         <v>2</v>
       </c>
     </row>
@@ -2320,7 +7215,7 @@
       <c r="A39" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39">
         <v>2</v>
       </c>
     </row>
@@ -2328,7 +7223,7 @@
       <c r="A40" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40">
         <v>75</v>
       </c>
     </row>
@@ -2336,7 +7231,7 @@
       <c r="A41" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41">
         <v>35</v>
       </c>
     </row>
@@ -2344,7 +7239,7 @@
       <c r="A42" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42">
         <v>40</v>
       </c>
     </row>
@@ -2352,7 +7247,7 @@
       <c r="A43" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43">
         <v>539</v>
       </c>
     </row>
@@ -2360,7 +7255,7 @@
       <c r="A44" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44">
         <v>164</v>
       </c>
     </row>
@@ -2368,7 +7263,7 @@
       <c r="A45" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45">
         <v>82</v>
       </c>
     </row>
@@ -2376,7 +7271,7 @@
       <c r="A46" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46">
         <v>82</v>
       </c>
     </row>
@@ -2384,7 +7279,7 @@
       <c r="A47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47">
         <v>178</v>
       </c>
     </row>
@@ -2392,7 +7287,7 @@
       <c r="A48" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48">
         <v>89</v>
       </c>
     </row>
@@ -2400,7 +7295,7 @@
       <c r="A49" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49">
         <v>89</v>
       </c>
     </row>
@@ -2408,7 +7303,7 @@
       <c r="A50" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50">
         <v>182</v>
       </c>
     </row>
@@ -2416,7 +7311,7 @@
       <c r="A51" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51">
         <v>91</v>
       </c>
     </row>
@@ -2424,7 +7319,7 @@
       <c r="A52" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B52" s="5">
+      <c r="B52">
         <v>91</v>
       </c>
     </row>
@@ -2432,7 +7327,7 @@
       <c r="A53" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B53">
         <v>15</v>
       </c>
     </row>
@@ -2440,7 +7335,7 @@
       <c r="A54" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B54" s="5">
+      <c r="B54">
         <v>5</v>
       </c>
     </row>
@@ -2448,7 +7343,7 @@
       <c r="A55" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B55">
         <v>10</v>
       </c>
     </row>
@@ -2456,25 +7351,22 @@
       <c r="A56" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B56" s="5"/>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B57" s="5"/>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B58" s="5"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B59" s="5">
+      <c r="B59">
         <v>780</v>
       </c>
     </row>
@@ -3166,4 +8058,681 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBB61701-0D5D-4B13-876D-DF8799AD3C71}">
+  <dimension ref="A1:O20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="11" width="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="5"/>
+      <c r="L1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="5"/>
+      <c r="N2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <f>_xlfn.STDEV.P(C3:J3)</f>
+        <v>0.18190244638266961</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D3">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="E3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F3">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="G3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="H3">
+        <v>1.9E-2</v>
+      </c>
+      <c r="I3">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="J3">
+        <v>1.4E-2</v>
+      </c>
+      <c r="K3">
+        <f>1-SUM(C3:J3)</f>
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <f>_xlfn.STDEV.P(C3:J3)</f>
+        <v>0.18190244638266961</v>
+      </c>
+      <c r="N3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3">
+        <f t="shared" ref="O3:O5" si="0">_xlfn.STDEV.P(C4:J4)</f>
+        <v>0.21023346397517212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="D4">
+        <v>0.248</v>
+      </c>
+      <c r="E4">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F4">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="G4">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="H4">
+        <v>0.01</v>
+      </c>
+      <c r="I4">
+        <v>3.9E-2</v>
+      </c>
+      <c r="J4">
+        <v>1.2E-2</v>
+      </c>
+      <c r="K4">
+        <f t="shared" ref="K4:K6" si="1">1-SUM(C4:J4)</f>
+        <v>-1.0000000000001119E-3</v>
+      </c>
+      <c r="L4">
+        <f t="shared" ref="L4:L6" si="2">_xlfn.STDEV.P(C4:J4)</f>
+        <v>0.21023346397517212</v>
+      </c>
+      <c r="N4" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="0"/>
+        <v>0.1854865224214417</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="D5">
+        <v>0.24</v>
+      </c>
+      <c r="E5">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="F5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G5">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="H5">
+        <v>0.04</v>
+      </c>
+      <c r="I5">
+        <v>1.6E-2</v>
+      </c>
+      <c r="J5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="2"/>
+        <v>0.1854865224214417</v>
+      </c>
+      <c r="N5" t="s">
+        <v>10</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="0"/>
+        <v>0.20701569988771382</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>0.61899999999999999</v>
+      </c>
+      <c r="D6">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="E6">
+        <v>1.4E-2</v>
+      </c>
+      <c r="F6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="H6">
+        <v>0.01</v>
+      </c>
+      <c r="I6">
+        <v>0.02</v>
+      </c>
+      <c r="J6">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="2"/>
+        <v>0.20701569988771382</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="C8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10">
+        <f>ROUND(12331/82439, 3)</f>
+        <v>0.15</v>
+      </c>
+      <c r="D10">
+        <f>ROUND(15546/82439, 3)</f>
+        <v>0.189</v>
+      </c>
+      <c r="E10">
+        <f>ROUND(6233/82439, 3)</f>
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="F10">
+        <f>ROUND(6177/82439, 3)</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G10">
+        <f>ROUND(7389/82439, 3)</f>
+        <v>0.09</v>
+      </c>
+      <c r="H10">
+        <f>ROUND(9344/82439, 3)</f>
+        <v>0.113</v>
+      </c>
+      <c r="I10">
+        <f>ROUND(12266/82439, 3)</f>
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="J10">
+        <f>ROUND(13153/82439, 3)</f>
+        <v>0.16</v>
+      </c>
+      <c r="K10">
+        <f>SUM(C10:J10)</f>
+        <v>1.002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <f>ROUND(363/1246, 3)</f>
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="D11">
+        <f>ROUND(269/1246, 3)</f>
+        <v>0.216</v>
+      </c>
+      <c r="E11">
+        <f>ROUND(60/1246, 3)</f>
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="F11">
+        <f>ROUND(32/1246, 3)</f>
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="G11">
+        <f>ROUND(58/1246, 3)</f>
+        <v>4.7E-2</v>
+      </c>
+      <c r="H11">
+        <f>ROUND(49/1246, 3)</f>
+        <v>3.9E-2</v>
+      </c>
+      <c r="I11">
+        <f>ROUND(246/1246, 3)</f>
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="J11">
+        <f>ROUND(169/1246, 3)</f>
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="K11">
+        <f>SUM(C11:J11)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <f>ROUND(387/3119, 3)</f>
+        <v>0.124</v>
+      </c>
+      <c r="D12">
+        <f>ROUND(349/3119, 3)</f>
+        <v>0.112</v>
+      </c>
+      <c r="E12">
+        <f>ROUND(244/3119, 3)</f>
+        <v>7.8E-2</v>
+      </c>
+      <c r="F12">
+        <f>ROUND(171/3119, 3)</f>
+        <v>5.5E-2</v>
+      </c>
+      <c r="G12">
+        <f>ROUND(703/3119, 3)</f>
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="H12">
+        <f>ROUND(657/3119, 3)</f>
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="I12">
+        <f>ROUND(405/3119, 3)</f>
+        <v>0.13</v>
+      </c>
+      <c r="J12">
+        <f>ROUND(203/3119, 3)</f>
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="K12">
+        <f>SUM(C12:J12)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="C15" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17">
+        <f>6000/48000</f>
+        <v>0.125</v>
+      </c>
+      <c r="D17">
+        <v>0.125</v>
+      </c>
+      <c r="E17">
+        <v>0.125</v>
+      </c>
+      <c r="F17">
+        <v>0.125</v>
+      </c>
+      <c r="G17">
+        <v>0.125</v>
+      </c>
+      <c r="H17">
+        <v>0.125</v>
+      </c>
+      <c r="I17">
+        <v>0.125</v>
+      </c>
+      <c r="J17">
+        <v>0.125</v>
+      </c>
+      <c r="K17">
+        <f t="shared" ref="K15:K21" si="3">SUM(C17:J17)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <f>ROUND(545/2188, 3)</f>
+        <v>0.249</v>
+      </c>
+      <c r="D18">
+        <f>ROUND(379/2188, 3)</f>
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="E18">
+        <f>ROUND(184/2188, 3)</f>
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="F18">
+        <f>ROUND(170/2188, 3)</f>
+        <v>7.8E-2</v>
+      </c>
+      <c r="G18">
+        <f>ROUND(175/2188, 3)</f>
+        <v>0.08</v>
+      </c>
+      <c r="H18">
+        <f>ROUND(154/2188, 3)</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I18">
+        <f>ROUND(322/2188, 3)</f>
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="J18">
+        <f>ROUND(259/2188, 3)</f>
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="3"/>
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19">
+        <f>ROUND(345/2897, 3)</f>
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="D19">
+        <f>ROUND(289/2897, 3)</f>
+        <v>0.1</v>
+      </c>
+      <c r="E19">
+        <f>ROUND(336/2897, 3)</f>
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="F19">
+        <f>ROUND(218/2897, 3)</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G19">
+        <f>ROUND(559/2897, 3)</f>
+        <v>0.193</v>
+      </c>
+      <c r="H19">
+        <f>ROUND(444/2897, 3)</f>
+        <v>0.153</v>
+      </c>
+      <c r="I19">
+        <f>ROUND(418/2897, 3)</f>
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="J19">
+        <f>ROUND(288/2897, 3)</f>
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="3"/>
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" t="s">
+        <v>25</v>
+      </c>
+      <c r="J20" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>